--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225267</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225364</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225287</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225473</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225315</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225317</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225268</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225273</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
           <t>NVI Stockfallet, Karlstads kommun, ink. fågel och dagfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106225274</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1967,6 +2027,11 @@
           <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98465909</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2100,6 +2165,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101851661</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123673266</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2330,6 +2405,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101851666</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2427,6 +2507,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124667767</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2572,6 +2657,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134028852</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2687,6 +2777,11 @@
           <t>Karlstads kommun - NVI Steffensminne</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114477634</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2802,6 +2897,11 @@
           <t>Karlstads kommun - NVI Steffensminne</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114477683</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
           <t>Karlstads kommun - NVI Steffensminne</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114477637</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3027,6 +3132,11 @@
           <t>Karlstads kommun - NVI Steffensminne</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114477619</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3142,6 +3252,11 @@
           <t>Karlstads kommun - NVI Steffensminne</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114477622</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3257,6 +3372,11 @@
           <t>Karlstads kommun - NVI Steffensminne</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114477700</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3373,6 +3493,11 @@
           <t>Karlstad kommun - Brungräsfjäril stockfallet</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119440642</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3489,6 +3614,11 @@
           <t>Karlstad kommun - Brungräsfjäril stockfallet</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119440643</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3608,6 +3738,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98002133</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3724,6 +3859,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119669864</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3839,6 +3979,11 @@
           <t>Karlstads kommun - NVI Reningsverk</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113904626</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3944,6 +4089,11 @@
           <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98465932</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4041,6 +4191,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57576259</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4166,6 +4321,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127911180</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4277,6 +4437,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57624957</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4388,6 +4553,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57624961</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4499,6 +4669,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57624963</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4610,6 +4785,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57624956</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4716,8 +4896,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57584703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119669864</v>
+        <v>136230934</v>
       </c>
       <c r="B28" t="n">
-        <v>57947</v>
+        <v>57979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,46 +3757,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stockfallet skogen, Fornåker, Edsgatan, Vrm</t>
+          <t>Finnmyrsgatan 11, Karlstadsområdet, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418018</v>
+        <v>418003</v>
       </c>
       <c r="R28" t="n">
-        <v>6587067</v>
+        <v>6586998</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3820,22 +3816,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3846,31 +3842,56 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mas Karin Gustafsson</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mas Karin Gustafsson</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119669864</t>
+          <t>https://artportalen.se/Sighting/136230934</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113904626</v>
+        <v>119669864</v>
       </c>
       <c r="B29" t="n">
-        <v>58636</v>
+        <v>57947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3878,21 +3899,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3900,29 +3921,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bråtetorp, Vrm</t>
+          <t>Stockfallet skogen, Fornåker, Edsgatan, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421892</v>
+        <v>418018</v>
       </c>
       <c r="R29" t="n">
-        <v>6586241</v>
+        <v>6587067</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3941,17 +3957,27 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Östra Fågelvik</t>
+          <t>Karlstad</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3966,53 +3992,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Mas Karin Gustafsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Karlstads kommun - NVI Reningsverk</t>
-        </is>
-      </c>
+          <t>Mas Karin Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113904626</t>
+          <t>https://artportalen.se/Sighting/119669864</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>98465932</v>
+        <v>113904626</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>58636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4020,19 +4042,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>kronoparken, Vrm</t>
+          <t>Bråtetorp, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420517</v>
+        <v>421892</v>
       </c>
       <c r="R30" t="n">
-        <v>6586101</v>
+        <v>6586241</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4051,17 +4083,17 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Karlstad</t>
+          <t>Östra Fågelvik</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4076,69 +4108,73 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
+          <t>Karlstads kommun - NVI Reningsverk</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98465932</t>
+          <t>https://artportalen.se/Sighting/113904626</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>57576259</v>
+        <v>98465932</v>
       </c>
       <c r="B31" t="n">
-        <v>96708</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Välsviken NE, S Gustaf Frödings gata, Vrm</t>
+          <t>kronoparken, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420557</v>
+        <v>420517</v>
       </c>
       <c r="R31" t="n">
-        <v>6585608</v>
+        <v>6586101</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4162,12 +4198,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2015-05-22</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4182,79 +4218,69 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Olof Persson, Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57576259</t>
+          <t>https://artportalen.se/Sighting/98465932</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127911180</v>
+        <v>57576259</v>
       </c>
       <c r="B32" t="n">
-        <v>56845</v>
+        <v>96708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100053</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gustaf Frödings gata, 656 38 Alster, Vrm</t>
+          <t>Välsviken NE, S Gustaf Frödings gata, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420500</v>
+        <v>420557</v>
       </c>
       <c r="R32" t="n">
-        <v>6585654</v>
+        <v>6585608</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4278,22 +4304,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>08:34</t>
+          <t>2015-05-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>08:34</t>
+          <t>2015-09-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,53 +4324,49 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Via Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Olof Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127911180</t>
+          <t>https://artportalen.se/Sighting/57576259</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>57624957</v>
+        <v>127911180</v>
       </c>
       <c r="B33" t="n">
-        <v>57953</v>
+        <v>56845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100053</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4367,24 +4379,24 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Välsviken, S Gustaf Frödings gata, Vrm</t>
+          <t>Gustaf Frödings gata, 656 38 Alster, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>420481</v>
+        <v>420500</v>
       </c>
       <c r="R33" t="n">
-        <v>6585613</v>
+        <v>6585654</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4408,12 +4420,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2015-05-22</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2015-09-16</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4428,44 +4450,48 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Olof Persson, Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57624957</t>
+          <t>https://artportalen.se/Sighting/127911180</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>57624961</v>
+        <v>57624957</v>
       </c>
       <c r="B34" t="n">
-        <v>58327</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4485,7 +4511,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4494,10 +4520,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>420517</v>
+        <v>420481</v>
       </c>
       <c r="R34" t="n">
-        <v>6585695</v>
+        <v>6585613</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4555,13 +4581,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57624961</t>
+          <t>https://artportalen.se/Sighting/57624957</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>57624963</v>
+        <v>57624961</v>
       </c>
       <c r="B35" t="n">
         <v>58327</v>
@@ -4601,7 +4627,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4610,10 +4636,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>420613</v>
+        <v>420517</v>
       </c>
       <c r="R35" t="n">
-        <v>6585732</v>
+        <v>6585695</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4671,38 +4697,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57624963</t>
+          <t>https://artportalen.se/Sighting/57624961</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>57624956</v>
+        <v>57624963</v>
       </c>
       <c r="B36" t="n">
-        <v>58676</v>
+        <v>58327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4717,7 +4743,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4726,10 +4752,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>420663</v>
+        <v>420613</v>
       </c>
       <c r="R36" t="n">
-        <v>6585631</v>
+        <v>6585732</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4787,60 +4813,65 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57624956</t>
+          <t>https://artportalen.se/Sighting/57624963</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>57584703</v>
+        <v>57624956</v>
       </c>
       <c r="B37" t="n">
-        <v>40300</v>
+        <v>58676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>214803</v>
+        <v>103055</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Välsviken NE, S Gustaf Frödings gata, Vrm</t>
+          <t>Välsviken, S Gustaf Frödings gata, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>420565</v>
+        <v>420663</v>
       </c>
       <c r="R37" t="n">
-        <v>6585581</v>
+        <v>6585631</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4892,11 +4923,122 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Olof Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57624956</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>57584703</v>
+      </c>
+      <c r="B38" t="n">
+        <v>40300</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Välsviken NE, S Gustaf Frödings gata, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>420565</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6585581</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2015-05-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2015-09-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Olof Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/57584703</t>
         </is>
@@ -4940,6 +5082,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -3749,7 +3749,7 @@
         <v>136230934</v>
       </c>
       <c r="B28" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -3749,7 +3749,7 @@
         <v>136230934</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -3749,7 +3749,7 @@
         <v>136230934</v>
       </c>
       <c r="B28" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -3749,7 +3749,7 @@
         <v>136230934</v>
       </c>
       <c r="B28" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -3749,7 +3749,7 @@
         <v>136230934</v>
       </c>
       <c r="B28" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
